--- a/docs/2. ppmp-template.xlsx
+++ b/docs/2. ppmp-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patriach\Downloads\laravel\procurex\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877C8D10-4E82-4832-AD44-CC8898805942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86EBD212-E1E7-4F0A-B013-C7355D250B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
